--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,9 +788,592 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136931995</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vojmån, NV om Storseleby, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>584413</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7190489</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 ex. under tall.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre, talldominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136931995</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136931988</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vojmån, NV om Storseleby, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>584359</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7190265</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grenar på några granar. Bålar upp till 60 cm långa.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre, talldominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136931988</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136931994</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vojmån, NV om Storseleby, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>584346</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7190308</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grenar i gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre, talldominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136931994</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136931996</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vojmån, NV om Storseleby, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>584460</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7190571</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grenar i nägra granar.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre, talldominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136931996</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136931992</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98221</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vojmån, NV om Storseleby, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>584275</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7190258</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0,5 m2.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre, talldominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136931992</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Pär Eriksson</t>
+          <t>Pär Eriksson, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Pär Eriksson</t>
+          <t>Pär Eriksson, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Pär Eriksson</t>
+          <t>Pär Eriksson, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Pär Eriksson</t>
+          <t>Pär Eriksson, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Pär Eriksson</t>
+          <t>Pär Eriksson, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pär Eriksson, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pär Eriksson, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pär Eriksson, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pär Eriksson, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pär Eriksson, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98302</v>
+        <v>98303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38454-2026 artfynd.xlsx
+++ b/artfynd/A 38454-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136931995</v>
       </c>
       <c r="B3" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136931988</v>
       </c>
       <c r="B4" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136931994</v>
       </c>
       <c r="B5" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136931996</v>
       </c>
       <c r="B6" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136931992</v>
       </c>
       <c r="B7" t="n">
-        <v>98303</v>
+        <v>98306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
